--- a/artfynd/S 1177-2022 artfynd.xlsx
+++ b/artfynd/S 1177-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136424653</v>
       </c>
       <c r="B2" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1177-2022 artfynd.xlsx
+++ b/artfynd/S 1177-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136424653</v>
       </c>
       <c r="B2" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1177-2022 artfynd.xlsx
+++ b/artfynd/S 1177-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,10 +3283,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97081292</v>
+        <v>137487926</v>
       </c>
       <c r="B23" t="n">
-        <v>43426</v>
+        <v>43485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3321,16 +3321,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenarstubäcken, Vstm</t>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504074</v>
+        <v>504105</v>
       </c>
       <c r="R23" t="n">
-        <v>6585527</v>
+        <v>6585645</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3357,12 +3358,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3373,6 +3374,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3392,16 +3408,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081292</t>
+          <t>https://artportalen.se/Sighting/137487926</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97081293</v>
+        <v>137487927</v>
       </c>
       <c r="B24" t="n">
-        <v>43426</v>
+        <v>43485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3436,16 +3452,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenarstubäcken, Vstm</t>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504076</v>
+        <v>504098</v>
       </c>
       <c r="R24" t="n">
-        <v>6585520</v>
+        <v>6585645</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3472,12 +3489,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3488,6 +3505,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3507,13 +3539,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081293</t>
+          <t>https://artportalen.se/Sighting/137487927</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97081294</v>
+        <v>97081292</v>
       </c>
       <c r="B25" t="n">
         <v>43426</v>
@@ -3557,10 +3589,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504072</v>
+        <v>504074</v>
       </c>
       <c r="R25" t="n">
-        <v>6585516</v>
+        <v>6585527</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3622,13 +3654,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081294</t>
+          <t>https://artportalen.se/Sighting/97081292</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97081295</v>
+        <v>97081293</v>
       </c>
       <c r="B26" t="n">
         <v>43426</v>
@@ -3672,10 +3704,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504073</v>
+        <v>504076</v>
       </c>
       <c r="R26" t="n">
-        <v>6585515</v>
+        <v>6585520</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3737,13 +3769,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081295</t>
+          <t>https://artportalen.se/Sighting/97081293</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97081297</v>
+        <v>97081294</v>
       </c>
       <c r="B27" t="n">
         <v>43426</v>
@@ -3787,10 +3819,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504074</v>
+        <v>504072</v>
       </c>
       <c r="R27" t="n">
-        <v>6585513</v>
+        <v>6585516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3852,13 +3884,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081297</t>
+          <t>https://artportalen.se/Sighting/97081294</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97081299</v>
+        <v>97081295</v>
       </c>
       <c r="B28" t="n">
         <v>43426</v>
@@ -3902,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504070</v>
+        <v>504073</v>
       </c>
       <c r="R28" t="n">
-        <v>6585512</v>
+        <v>6585515</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3967,13 +3999,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081299</t>
+          <t>https://artportalen.se/Sighting/97081295</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97081300</v>
+        <v>97081297</v>
       </c>
       <c r="B29" t="n">
         <v>43426</v>
@@ -4017,10 +4049,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504069</v>
+        <v>504074</v>
       </c>
       <c r="R29" t="n">
-        <v>6585512</v>
+        <v>6585513</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4082,13 +4114,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97081300</t>
+          <t>https://artportalen.se/Sighting/97081297</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105553842</v>
+        <v>97081299</v>
       </c>
       <c r="B30" t="n">
         <v>43426</v>
@@ -4128,14 +4160,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stenarsstubäcken  Yta 7:12, Vstm</t>
+          <t>Stenarstubäcken, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504079</v>
+        <v>504070</v>
       </c>
       <c r="R30" t="n">
-        <v>6585502</v>
+        <v>6585512</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4162,17 +4194,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4183,21 +4210,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>ängsvädd</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Succisa pratensis</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Succisa pratensis</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4217,13 +4229,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105553842</t>
+          <t>https://artportalen.se/Sighting/97081299</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105553862</v>
+        <v>97081300</v>
       </c>
       <c r="B31" t="n">
         <v>43426</v>
@@ -4263,14 +4275,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stenarsstubäcken  Yta 7:12, Vstm</t>
+          <t>Stenarstubäcken, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504074</v>
+        <v>504069</v>
       </c>
       <c r="R31" t="n">
-        <v>6585509</v>
+        <v>6585512</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4297,17 +4309,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4318,21 +4325,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>ängsvädd</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Succisa pratensis</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Succisa pratensis</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4352,13 +4344,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105553862</t>
+          <t>https://artportalen.se/Sighting/97081300</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120768523</v>
+        <v>105553842</v>
       </c>
       <c r="B32" t="n">
         <v>43426</v>
@@ -4396,21 +4388,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+          <t>Stenarsstubäcken  Yta 7:12, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504061</v>
+        <v>504079</v>
       </c>
       <c r="R32" t="n">
-        <v>6585514</v>
+        <v>6585502</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,12 +4424,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4454,14 +4446,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>ängsvädd</t>
         </is>
       </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>ängsvädd</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4482,13 +4479,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120768523</t>
+          <t>https://artportalen.se/Sighting/105553842</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120768525</v>
+        <v>105553862</v>
       </c>
       <c r="B33" t="n">
         <v>43426</v>
@@ -4526,21 +4523,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+          <t>Stenarsstubäcken  Yta 7:12, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504061</v>
+        <v>504074</v>
       </c>
       <c r="R33" t="n">
-        <v>6585520</v>
+        <v>6585509</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4567,12 +4559,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,14 +4581,19 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AL33" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>ängsvädd</t>
         </is>
       </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>ängsvädd</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4612,13 +4614,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120768525</t>
+          <t>https://artportalen.se/Sighting/105553862</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120768527</v>
+        <v>120768523</v>
       </c>
       <c r="B34" t="n">
         <v>43426</v>
@@ -4667,10 +4669,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504060</v>
+        <v>504061</v>
       </c>
       <c r="R34" t="n">
-        <v>6585519</v>
+        <v>6585514</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4742,13 +4744,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120768527</t>
+          <t>https://artportalen.se/Sighting/120768523</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120768543</v>
+        <v>120768525</v>
       </c>
       <c r="B35" t="n">
         <v>43426</v>
@@ -4797,10 +4799,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504098</v>
+        <v>504061</v>
       </c>
       <c r="R35" t="n">
-        <v>6585639</v>
+        <v>6585520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4872,13 +4874,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120768543</t>
+          <t>https://artportalen.se/Sighting/120768525</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120768544</v>
+        <v>120768527</v>
       </c>
       <c r="B36" t="n">
         <v>43426</v>
@@ -4927,10 +4929,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504100</v>
+        <v>504060</v>
       </c>
       <c r="R36" t="n">
-        <v>6585639</v>
+        <v>6585519</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5002,13 +5004,13 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120768544</t>
+          <t>https://artportalen.se/Sighting/120768527</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129834613</v>
+        <v>120768543</v>
       </c>
       <c r="B37" t="n">
         <v>43426</v>
@@ -5057,10 +5059,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504072</v>
+        <v>504098</v>
       </c>
       <c r="R37" t="n">
-        <v>6585512</v>
+        <v>6585639</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5087,12 +5089,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5104,19 +5106,14 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>ängsvädd</t>
         </is>
       </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Succisa pratensis</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Succisa pratensis</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5137,13 +5134,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129834613</t>
+          <t>https://artportalen.se/Sighting/120768543</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129834614</v>
+        <v>120768544</v>
       </c>
       <c r="B38" t="n">
         <v>43426</v>
@@ -5192,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504073</v>
+        <v>504100</v>
       </c>
       <c r="R38" t="n">
-        <v>6585510</v>
+        <v>6585639</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5222,12 +5219,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5239,19 +5236,14 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
+      <c r="AL38" t="inlineStr">
         <is>
           <t>ängsvädd</t>
         </is>
       </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Succisa pratensis</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Succisa pratensis</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5272,13 +5264,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129834614</t>
+          <t>https://artportalen.se/Sighting/120768544</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129834615</v>
+        <v>129834613</v>
       </c>
       <c r="B39" t="n">
         <v>43426</v>
@@ -5330,7 +5322,7 @@
         <v>504072</v>
       </c>
       <c r="R39" t="n">
-        <v>6585511</v>
+        <v>6585512</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5407,13 +5399,13 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129834615</t>
+          <t>https://artportalen.se/Sighting/129834613</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129834616</v>
+        <v>129834614</v>
       </c>
       <c r="B40" t="n">
         <v>43426</v>
@@ -5462,10 +5454,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504063</v>
+        <v>504073</v>
       </c>
       <c r="R40" t="n">
-        <v>6585517</v>
+        <v>6585510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5542,7 +5534,670 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/129834614</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129834615</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43426</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>504072</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6585511</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834615</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129834616</v>
+      </c>
+      <c r="B42" t="n">
+        <v>43426</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>504063</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6585517</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129834616</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137487881</v>
+      </c>
+      <c r="B43" t="n">
+        <v>43485</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>504063</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6585515</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>åkervädd</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137487881</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137487882</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43485</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>504065</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6585493</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>åkervädd</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137487882</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137487885</v>
+      </c>
+      <c r="B45" t="n">
+        <v>43485</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stenarsstubäcken Yta 7:12, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>504067</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6585492</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>åkervädd</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Knautia arvensis</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137487885</t>
         </is>
       </c>
     </row>
@@ -5587,6 +6242,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
